--- a/docs/materials/functions_and_arguments.xlsx
+++ b/docs/materials/functions_and_arguments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\proj\ROAD\road\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\proj\ROAD\road\docs\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0EA404-6DAA-46D9-98DD-6DA0999729D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EFC142-EA16-480E-8695-A6C8FDA8F951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="96">
   <si>
     <t>road_get_localities()</t>
   </si>
@@ -421,6 +421,12 @@
       </rPr>
       <t xml:space="preserve"> Fuzzy search type (contains term)</t>
     </r>
+  </si>
+  <si>
+    <t>road_get_sql()</t>
+  </si>
+  <si>
+    <t>query</t>
   </si>
 </sst>
 </file>
@@ -542,7 +548,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -565,11 +571,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -610,6 +690,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -632,6 +715,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,57 +1029,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA191576-E575-4853-A1BC-43BBBFBC35B4}">
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="3.7109375" style="8" customWidth="1"/>
     <col min="3" max="3" width="33.140625" style="8" customWidth="1"/>
-    <col min="4" max="30" width="3.7109375" style="8" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="8"/>
+    <col min="4" max="32" width="3.7109375" style="8" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="16" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16" t="s">
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="28"/>
     </row>
-    <row r="2" spans="1:30" ht="159" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+    <row r="2" spans="1:32" ht="159" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="9" t="s">
         <v>42</v>
       </c>
@@ -1050,9 +1163,13 @@
       <c r="AD2" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="AE2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="11">
@@ -1105,11 +1222,13 @@
       <c r="AA3" s="13"/>
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
-      <c r="AD3" s="13"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="30"/>
     </row>
-    <row r="4" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+    <row r="4" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="26"/>
+      <c r="B4" s="19" t="s">
         <v>91</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1159,11 +1278,13 @@
       <c r="AA4" s="13"/>
       <c r="AB4" s="14"/>
       <c r="AC4" s="14"/>
-      <c r="AD4" s="13"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="30"/>
     </row>
-    <row r="5" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19"/>
+    <row r="5" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="26"/>
+      <c r="B5" s="20"/>
       <c r="C5" s="12" t="s">
         <v>87</v>
       </c>
@@ -1215,11 +1336,13 @@
         <v>30</v>
       </c>
       <c r="AC5" s="14"/>
-      <c r="AD5" s="13"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="30"/>
     </row>
-    <row r="6" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="17"/>
-      <c r="B6" s="19"/>
+    <row r="6" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="26"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="12" t="s">
         <v>88</v>
       </c>
@@ -1273,11 +1396,13 @@
         <v>30</v>
       </c>
       <c r="AC6" s="14"/>
-      <c r="AD6" s="13"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="30"/>
     </row>
-    <row r="7" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+    <row r="7" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="26"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="12" t="s">
         <v>5</v>
       </c>
@@ -1329,11 +1454,13 @@
         <v>30</v>
       </c>
       <c r="AC7" s="14"/>
-      <c r="AD7" s="13"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="30"/>
     </row>
-    <row r="8" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="19"/>
+    <row r="8" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="26"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="12" t="s">
         <v>6</v>
       </c>
@@ -1385,11 +1512,13 @@
         <v>30</v>
       </c>
       <c r="AC8" s="14"/>
-      <c r="AD8" s="13"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="30"/>
     </row>
-    <row r="9" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+    <row r="9" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="26"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="12" t="s">
         <v>89</v>
       </c>
@@ -1441,11 +1570,13 @@
         <v>30</v>
       </c>
       <c r="AC9" s="14"/>
-      <c r="AD9" s="13"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="30"/>
     </row>
-    <row r="10" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="17"/>
-      <c r="B10" s="19"/>
+    <row r="10" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="26"/>
+      <c r="B10" s="20"/>
       <c r="C10" s="12" t="s">
         <v>8</v>
       </c>
@@ -1497,11 +1628,13 @@
         <v>30</v>
       </c>
       <c r="AC10" s="14"/>
-      <c r="AD10" s="13"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="30"/>
     </row>
-    <row r="11" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
+    <row r="11" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="26"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="12" t="s">
         <v>9</v>
       </c>
@@ -1555,11 +1688,13 @@
         <v>30</v>
       </c>
       <c r="AC11" s="14"/>
-      <c r="AD11" s="13"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="30"/>
     </row>
-    <row r="12" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="17"/>
-      <c r="B12" s="19"/>
+    <row r="12" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="26"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
@@ -1613,11 +1748,13 @@
         <v>30</v>
       </c>
       <c r="AC12" s="14"/>
-      <c r="AD12" s="13"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="30"/>
     </row>
-    <row r="13" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
+    <row r="13" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="26"/>
+      <c r="B13" s="20"/>
       <c r="C13" s="12" t="s">
         <v>11</v>
       </c>
@@ -1675,11 +1812,13 @@
         <v>30</v>
       </c>
       <c r="AC13" s="14"/>
-      <c r="AD13" s="13"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="30"/>
     </row>
-    <row r="14" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18" t="s">
+    <row r="14" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="26"/>
+      <c r="B14" s="19" t="s">
         <v>92</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -1714,10 +1853,12 @@
       </c>
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
+      <c r="AE14" s="14"/>
+      <c r="AF14" s="31"/>
     </row>
-    <row r="15" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
+    <row r="15" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="26"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="12" t="s">
         <v>90</v>
       </c>
@@ -1752,24 +1893,24 @@
       <c r="AD15" s="13" t="s">
         <v>30</v>
       </c>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="30"/>
     </row>
-    <row r="16" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="10"/>
+    <row r="16" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="27"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+        <v>94</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="14"/>
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
@@ -1786,14 +1927,20 @@
       <c r="Z16" s="14"/>
       <c r="AA16" s="14"/>
       <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF16" s="30"/>
     </row>
-    <row r="17" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="17"/>
+    <row r="17" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="18" t="s">
+        <v>76</v>
+      </c>
       <c r="B17" s="10"/>
       <c r="C17" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
@@ -1822,16 +1969,54 @@
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
       <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="31"/>
+    </row>
+    <row r="18" spans="1:32" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="18"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="M1:AD1"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="B4:B13"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A3:A15"/>
     <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A3:A16"/>
+    <mergeCell ref="M1:AE1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1851,82 +2036,82 @@
     <row r="1" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22" t="s">
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="23"/>
-      <c r="AR1" s="23"/>
-      <c r="AS1" s="23"/>
-      <c r="AT1" s="23"/>
-      <c r="AU1" s="23"/>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23"/>
-      <c r="AX1" s="23"/>
-      <c r="AY1" s="23"/>
-      <c r="AZ1" s="23"/>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="22"/>
-      <c r="BD1" s="22"/>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="22"/>
-      <c r="BG1" s="22"/>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
-      <c r="BJ1" s="22"/>
-      <c r="BK1" s="22"/>
-      <c r="BL1" s="23"/>
-      <c r="BM1" s="23"/>
-      <c r="BN1" s="23"/>
-      <c r="BO1" s="23"/>
-      <c r="BP1" s="23"/>
-      <c r="BQ1" s="23"/>
-      <c r="BR1" s="23"/>
-      <c r="BS1" s="23"/>
-      <c r="BT1" s="23"/>
-      <c r="BU1" s="23"/>
-      <c r="BV1" s="23"/>
-      <c r="BW1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="23"/>
+      <c r="AJ1" s="23"/>
+      <c r="AK1" s="23"/>
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="24"/>
+      <c r="AN1" s="24"/>
+      <c r="AO1" s="24"/>
+      <c r="AP1" s="24"/>
+      <c r="AQ1" s="24"/>
+      <c r="AR1" s="24"/>
+      <c r="AS1" s="24"/>
+      <c r="AT1" s="24"/>
+      <c r="AU1" s="24"/>
+      <c r="AV1" s="24"/>
+      <c r="AW1" s="24"/>
+      <c r="AX1" s="24"/>
+      <c r="AY1" s="24"/>
+      <c r="AZ1" s="24"/>
+      <c r="BB1" s="23"/>
+      <c r="BC1" s="23"/>
+      <c r="BD1" s="23"/>
+      <c r="BE1" s="23"/>
+      <c r="BF1" s="23"/>
+      <c r="BG1" s="23"/>
+      <c r="BH1" s="23"/>
+      <c r="BI1" s="23"/>
+      <c r="BJ1" s="23"/>
+      <c r="BK1" s="23"/>
+      <c r="BL1" s="24"/>
+      <c r="BM1" s="24"/>
+      <c r="BN1" s="24"/>
+      <c r="BO1" s="24"/>
+      <c r="BP1" s="24"/>
+      <c r="BQ1" s="24"/>
+      <c r="BR1" s="24"/>
+      <c r="BS1" s="24"/>
+      <c r="BT1" s="24"/>
+      <c r="BU1" s="24"/>
+      <c r="BV1" s="24"/>
+      <c r="BW1" s="24"/>
     </row>
     <row r="2" spans="1:75" ht="219" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2114,7 +2299,7 @@
       <c r="BW2" s="4"/>
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2223,7 +2408,7 @@
       <c r="BW3" s="6"/>
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2338,7 +2523,7 @@
       <c r="BW4" s="5"/>
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2459,7 +2644,7 @@
       <c r="BW5" s="5"/>
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2580,7 +2765,7 @@
       <c r="BW6" s="5"/>
     </row>
     <row r="7" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2703,7 +2888,7 @@
       <c r="BW7" s="5"/>
     </row>
     <row r="8" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2828,7 +3013,7 @@
       <c r="BW8" s="5"/>
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2945,7 +3130,7 @@
       <c r="BW9" s="5"/>
     </row>
     <row r="10" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3066,7 +3251,7 @@
       <c r="BW10" s="5"/>
     </row>
     <row r="11" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -3193,7 +3378,7 @@
       <c r="BW11" s="5"/>
     </row>
     <row r="12" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3312,7 +3497,7 @@
       <c r="BW12" s="5"/>
     </row>
     <row r="13" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -3435,7 +3620,7 @@
       <c r="BW13" s="5"/>
     </row>
     <row r="14" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
